--- a/docs/150526_enhancement_status.xlsx
+++ b/docs/150526_enhancement_status.xlsx
@@ -518,14 +518,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -573,7 +573,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Placeholder cpc-logo.png still in place; awaiting hi-res asset from Saad. Logo plumbing already in place at both desktop/src/features/HomePage.tsx and desktop/src/features/AppShell.tsx (sidebar footer).</t>
+          <t>Placeholder cpc-logo.png in place; awaiting hi-res asset from Saad. Logo slots ready at desktop/src/features/HomePage.tsx and the sidebar footer in AppShell.tsx.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Net-new workflow stage. Open questions: position in flow (before or after upload?), backend support, multi-tenant data persistence per BU.</t>
+          <t>Net-new workflow stage. See the Open discussion sheet for the open questions.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Removed Workforce Studio label and alt text. Logo moved from sidebar header to sidebar footer (above engine status).</t>
+          <t>Removed Workforce Studio label and alt. Logo moved from sidebar header to sidebar footer above engine status.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Data Upload — Remove 'Upload workbook' from left-panel bottom</t>
+          <t>Data Upload — Before upload, change subtitle to 'Upload In-house and Outsourced Employees Payroll in one [Excel workbook]'</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Button label shortened: 'Upload workbook' / 'Upload new workbook' → 'Upload' / 'Upload new'.</t>
+          <t>Subtitle updated. Final wording uses 'Excel workbook' rather than 'XLS file' because the app accepts .xlsx only (modern OOXML); .xls (legacy BIFF) is rejected by the validator.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>commit 1 / AppShell.tsx</t>
+          <t>commits 8 + 11 / UploadWorkspace.tsx</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Data Upload — After upload, single 'Data Loaded' message (not duplicate 'workbook loaded')</t>
+          <t>Data Upload — Remove 'Upload workbook' from left-panel bottom</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Section eyebrow renamed to 'Data Loaded'. Subtitle row replaced with the loaded workbook filename so the header is informative without duplication.</t>
+          <t>Button label shortened: 'Upload workbook' / 'Upload new workbook' → 'Upload' / 'Upload new'.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>commit 2 / UploadWorkspace.tsx</t>
+          <t>commit 1 / AppShell.tsx</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Data Upload — Rename 'Subcontracted' → 'Outsourced'</t>
+          <t>Data Upload — After upload, single 'Data Loaded' message (not duplicate 'workbook loaded')</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>UI label updated on the metric card. NOT changed: the Excel SHEET NAME 'Subcontractor' (user file format requirement) and internal API field names (would break client compatibility).</t>
+          <t>Section eyebrow renamed to 'Data Loaded'. Subtitle row replaced with the loaded workbook filename so the header is informative without duplication.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Data Upload — Reorganize boxes (total full width on top, then in-house / outsourced / job families row)</t>
+          <t>Data Upload — Rename 'Subcontracted' → 'Outsourced'</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>New data-health-total class for the full-width total card; data-health-grid--triple for the 3-card row below.</t>
+          <t>UI label updated on the metric card. NOT changed: the Excel SHEET NAME 'Subcontractor' (user file format requirement) and internal API field names (would break client compatibility).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>commit 2 / UploadWorkspace.tsx + styles.css</t>
+          <t>commit 2 / UploadWorkspace.tsx</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Additional Inputs — No need for 'Brand new' on this sheet</t>
+          <t>Data Upload — Reorganize boxes (total full width on top, then in-house / outsourced / job families row)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>All 'brand-new family' wording stripped from button labels, wizard titles, and metadata rows.</t>
+          <t>New data-health-total class for the full-width total card; data-health-grid--triple for the 3-card row below.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>commit 3 / MappingResolveWorkspace.tsx</t>
+          <t>commit 2 / UploadWorkspace.tsx + styles.css</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Additional Inputs — Add 'Job' to all 'families' (Add a Job Family, Name of job family, etc.)</t>
+          <t>Additional Inputs — No need for 'Brand new' on this sheet</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Custom families → Custom job families. Family name → Name of job family. Edit family → Edit job family. Define family from selected → Define job family from selected.</t>
+          <t>All 'brand-new family' wording stripped from button labels, wizard titles, and metadata rows.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Additional Inputs — '1 Custom' badge persistence across app restarts?</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Answered (info)</t>
+          <t>Additional Inputs — Add 'Job' to all 'families'</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Desktop React ALREADY persists custom families across restarts via localStorage (see App.tsx persistGet/persistSet on 'custom_families'). Streamlit is session-only — Streamlit was out of scope for this PR so no change there.</t>
+          <t>Custom families → Custom job families. Family name → Name of job family. Edit family → Edit job family. Define family from selected → Define job family from selected.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>commit 3 / MappingResolveWorkspace.tsx</t>
         </is>
       </c>
     </row>
@@ -887,22 +887,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>User Assumption — No workbook/data-loaded window on top</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Additional Inputs — '1 Custom' badge persistence across app restarts?</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Answered (info)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Upload metrics card no longer renders on the Ready (User Assumptions) stage; UploadWorkspace is now upload-stage-only.</t>
+          <t>Desktop React ALREADY persists custom families across restarts via localStorage (App.tsx persistGet/persistSet on 'custom_families'). Streamlit is session-only — Streamlit out of scope for this PR.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>commit 2 / App.tsx</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>User Assumption — Drop repeated 'User assumptions'; just 'Optimization Mode' with two radio options</t>
+          <t>User Assumption — No workbook/data-loaded window on top</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>In-content 'User Assumptions' eyebrow removed; the topbar's 'USER ASSUMPTIONS' green tab title remains as the single source of truth. Two-mode toggle preserved.</t>
+          <t>Upload metrics card no longer renders on the Ready stage; UploadWorkspace is upload-stage-only.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>commit 4 / ScenarioControls.tsx</t>
+          <t>commit 2 / App.tsx</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>User Assumption — If Target plan selected, show Target Manpower Plan window</t>
+          <t>User Assumption — Drop repeated 'User assumptions'; just 'Optimization Mode' with two radio options</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Already conditional (isTargetMode). Verified after the User Assumptions header cleanup. Auto-opens the target accordion when the mode toggles.</t>
+          <t>In-content 'User Assumptions' eyebrow removed; the topbar's 'USER ASSUMPTIONS' tab title is the single source of truth.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>no change needed</t>
+          <t>commit 4 / ScenarioControls.tsx</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>All Tabs — Remove second row in upper white strip; keep title in green, larger</t>
+          <t>User Assumption — If Target plan selected, show Target Manpower Plan window</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -978,51 +978,51 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Topbar collapses to a single row. Green eyebrow promoted to a 22px display-font heading; subtitle row removed. Same treatment across Data Upload / Additional Inputs / User Assumptions / Output.</t>
+          <t>Already conditional (isTargetMode). Verified after the User Assumptions header cleanup. Auto-opens the target accordion when the mode toggles.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>commit 1 / AppShell.tsx + styles.css</t>
+          <t>no change needed</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>After homepage — list of companies with 'to be configured', click MGIC; tab 'BU Selection'</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Deferred (discussion)</t>
+          <t>User Assumption — Rename 'Assumption and Input' section to just 'Inputs'</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Same as the Look &amp; Feel BU Selection entry — net-new stage that needs a design pass. Risk noted: tool currently assumes one BU per laptop.</t>
+          <t>The inner SectionHeader for the inputs panel was reduced to title='Inputs' (no eyebrow). The 'Assumptions' eyebrow disappeared in commit 4.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>follow-up PR</t>
+          <t>commit 4 / ScenarioControls.tsx</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Reduce processing time after upload</t>
+          <t>User Assumption — All input windows closed by default (no first one open)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1032,78 +1032,78 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>94.06s → 19.25s on Manpower.xlsx (~4.9× faster). Root cause: normalize_lookup_text called 16.3M times and per-row dict rebuilds in get_numeric_from_row. Fix: lru_cache + hoist the per-DataFrame column resolver. Cache hit rate 99.94%. All tests still pass.</t>
+          <t>openSections initial state set to new Set(); user can scan all category headings before opening any. Target Manpower Plan still auto-opens when target mode is selected.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>commit 7 / manpower_app/utils.py</t>
+          <t>commit 8 / ScenarioControls.tsx</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>After XLS processing — why is 'add a job family' visible? (discuss)</t>
+          <t>User Assumption — Recategorize inputs: (1) Saudization, (2) Outsourced Employees, (3) Workforce Protection</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Done (resolved by hiding outside Target mode)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Button now only appears when 'Input and Optimize a Target Manpower Plan' is selected, with a short hint explaining the flow. In Current mode it's hidden — a family with no payroll rows has nothing to optimize.</t>
+          <t>Replaced the previous (Saudization &amp; Risk) + (Workforce Protection) + (Advanced Settings) layout with the three top-level categories. Hard Inputs (ratio overrides) remains as a separate fourth accordion.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>commit 6 / MappingResolveWorkspace.tsx + App.tsx</t>
+          <t>commit 9 / ScenarioControls.tsx</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Make Outsourceable / Fully Inhouse / Partially Outsourceable dynamic</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Deferred (discussion)</t>
+          <t>User Assumption — Saudization subsections: A) Overall, B) By Job Family (side-by-side)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Currently hardcoded in manpower_app/rules.py (OUTSOURCEABILITY_RULES dict). Open question: source for dynamic values — workbook column, in-app editor, or both? Affects rules, costs, optimization constraints. Backend rework required.</t>
+          <t>Two-column grid (.scenario-two-column, collapses to 1 column under 980px). A = enforce + overall rate + Saudi cost premium. B = engineer/sales/management rates.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>follow-up PR</t>
+          <t>commit 9 / ScenarioControls.tsx + styles.css</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Tool should handle Saudis-cheaper-than-non-Saudis (auto-correct)</t>
+          <t>User Assumption — Outsourced Employees subsections: A) Risk Factor with (ⓘ) tooltip, B) Renegotiated Rate (side-by-side)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1113,78 +1113,78 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Saudi cost premium floored at 1.0× in three places (defense in depth): desktop slider min, manpower_api Pydantic validator, and manpower_app.costs.calculate_inhouse_cost_split. Saudis can no longer be configured as cheaper than non-Saudis from any code path.</t>
+          <t>A = risk factor slider with an info pill explaining the haircut math. B = negotiated-rates toggle reveals insurance/service margin, plus Override outsource cost + discount slider (moved here from Advanced).</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>commit 4 / costs.py + ScenarioControls.tsx + app.py</t>
+          <t>commit 9 / ScenarioControls.tsx + styles.css</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Hard inputs — edit ratio AND driver name (e.g., quarries labor vs quarries skilled labor)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Deferred (discussion)</t>
+          <t>User Assumption — Workforce Protection: hide in Target mode; rename + flip 'Allow reducing Saudi headcount' → 'Protect Current Saudis'</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Driver mappings are hardcoded in manpower_app/ratios.py:calculate_driver_values. Making this user-editable needs the same backend pattern as the dynamic-outsourceability item: new settings field, new API contract, propagation through the LP. Best done with #20.</t>
+          <t>Accordion is hidden entirely when optimization_mode === 'target'. Toggle label is renamed and the semantics are inverted: checked = protect (the safer default). Parallel to 'Protect tenured employees' below.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>follow-up PR</t>
+          <t>commits 8 + 9 / ScenarioControls.tsx</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Target plan — ask about drivers so ratios can be recalculated</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Deferred (discussion)</t>
+          <t>All Tabs — Bottom navigation arrows (Prev / Next)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Depends on the editable-driver work (#22). Once a user can pin which profession is the ratio driver, the target plan UI needs an input for the driver headcount.</t>
+          <t>StageNav component at the foot of each content stage. Buttons disable when the prev/next stage is unreachable. Labels show the destination stage rather than just an arrow.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>follow-up PR</t>
+          <t>commit 10 / AppShell.tsx + styles.css</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Debugging</t>
+          <t>Look &amp; Feel</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Risk input slider — should reach zero</t>
+          <t>All Tabs — Remove second row in upper white strip; keep title in green, larger</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1194,37 +1194,253 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Slider min lowered from 0.01 to 0 in both UI (ScenarioControls.tsx) and API (Pydantic gt=0 → ge=0). At R=0 the LP constraint degenerates cleanly to O+I ≥ M; the rearranged closed-form (T−M)/R is only consulted when R&gt;0. README updated.</t>
+          <t>Topbar collapses to a single row. Green eyebrow promoted to a 22px display-font heading; subtitle row removed.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>commit 4 / ScenarioControls.tsx + app.py + README.md</t>
+          <t>commit 1 / AppShell.tsx + styles.css</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>After homepage — list of companies; click MGIC; tab 'BU Selection'</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Deferred (discussion)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Net-new stage that needs a design pass. Risk noted in the spec: tool currently assumes one BU per laptop.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>follow-up PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Reduce processing time after upload</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>94.06s → 19.25s on Manpower.xlsx (~4.9× faster). Root cause: normalize_lookup_text called 16.3M times and per-row dict rebuilds in get_numeric_from_row. Fix: lru_cache + hoist the per-DataFrame column resolver. Cache hit rate 99.94%. All tests still pass. Remaining cost is pandas .apply row iteration + openpyxl XML parsing — bigger refactors deferred.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>commit 7 / manpower_app/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>After XLS processing — why is 'add a job family' visible?</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Done (Target mode only)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Button now only appears when 'Input and Optimize a Target Manpower Plan' is selected, with a short hint explaining the flow. Hidden in Current mode — adding a family with no payroll rows has nothing to optimize.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>commit 6 / MappingResolveWorkspace.tsx + App.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Make Outsourceable / Fully Inhouse / Partially Outsourceable dynamic</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Deferred (discussion)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Currently hardcoded in manpower_app/rules.py. Backend rework required: source (workbook column vs in-app editor), API contract, propagation through rules/costs/LP.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>follow-up PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Saudis-cheaper-than-non-Saudis (auto-correct)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Saudi cost premium floored at 1.0× in three places (defense in depth): desktop slider min, manpower_api Pydantic validator, and manpower_app.costs.calculate_inhouse_cost_split. Saudis can no longer be configured as cheaper than non-Saudis from any code path.</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>commit 4 / costs.py + ScenarioControls.tsx + app.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Hard inputs — edit ratio AND driver name (e.g., quarries labor vs skilled labor)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Deferred (discussion)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Driver mappings are hardcoded in manpower_app/ratios.py:calculate_driver_values. Same backend pattern as the dynamic-outsourceability item: new settings field, new API contract, propagation through the LP. Best done with the previous item.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>follow-up PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Target plan — ask about drivers so ratios can be recalculated</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Deferred (discussion)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Depends on the editable-driver work above. Once a user can pin which profession is the ratio driver, the target plan UI needs an input for the driver headcount.</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>follow-up PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>Debugging</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Risk input slider — should reach zero</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Slider min lowered from 0.01 to 0 in UI and API. At R=0 the LP constraint degenerates cleanly to O+I ≥ M; the rearranged closed-form (T−M)/R is only consulted when R&gt;0. README updated.</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>commit 4 / ScenarioControls.tsx + app.py + README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Debugging</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>All tabs — '0' doesn't get deleted in number inputs</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Replaced controlled &lt;input type='number'&gt; with NumericTextInput (type='text' + inputMode='decimal') backed by an internal text buffer. On focus the value is selected; first keystroke replaces 0 cleanly across all browsers. Also accepts optional value/placeholder so the target-headcount field can show empty + a 'current headcount' placeholder.</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Replaced controlled &lt;input type='number'&gt; with NumericTextInput (type='text' + inputMode='decimal') backed by a text buffer. First keystroke replaces 0 cleanly. Supports optional value/placeholder for the target-headcount field.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>commits 5 + 6 / ScenarioControls.tsx</t>
         </is>
@@ -1245,7 +1461,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1256,7 +1472,7 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>150526_Manpower Optimization Tool Enhancements.xlsx</t>
+          <t>150526_Manpower Optimization Tool Enhancements (1).xlsx</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1519,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1313,7 +1529,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1404,14 +1620,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Net-new workflow stage. Spec hints 'after homepage, list of companies, click MGIC' but the same line flags the assumption risk: 'they will always run the app on one laptop'. Needs a design pass.</t>
+          <t>Net-new workflow stage. Spec hints 'after homepage, list of companies, click MGIC' but the same line flags the assumption risk: 'they will always run the app on one laptop'.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>1. Where does BU Selection sit in the workflow (before upload, after upload, side-panel)?
 2. Is the company list driven by data (a config workbook?) or hardcoded?
-3. Do we need per-BU data persistence (different workbooks loaded per BU)?
+3. Do we need per-BU data persistence?
 4. Multi-user / multi-machine collaboration implications.</t>
         </is>
       </c>
@@ -1441,14 +1657,14 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Currently OUTSOURCEABILITY_RULES is hardcoded across 40 job families in manpower_app/rules.py. Making this dynamic affects rules → costs → optimization constraints.</t>
+          <t>Currently OUTSOURCEABILITY_RULES is hardcoded across 40 job families in manpower_app/rules.py. Affects rules → costs → optimization constraints.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>1. Source: workbook column, in-app editor, or both?
 2. Per-BU overrides (ties into #4)?
-3. Validation: how to prevent inconsistent states (Fully Outsourceable + a non-zero ratio override)?</t>
+3. Validation: prevent inconsistent states (Fully Outsourceable + a non-zero ratio override).</t>
         </is>
       </c>
     </row>
@@ -1465,8 +1681,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1. UI: free-text label vs structured (activity + profession) picker?
-2. Backend: new settings field driver_overrides — needs propagation through calculate_driver_values, the API, and the LP.
+          <t>1. UI: free-text label vs structured picker (activity + profession)?
+2. Backend: new settings field driver_overrides — needs propagation through calculate_driver_values, API, and LP.
 3. Should this share data with the partial-config 'driver-based' option in the custom-family wizard?</t>
         </is>
       </c>
@@ -1479,7 +1695,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Requires #22 first. Once driver is editable, the target plan needs an input field for the driver headcount so ratios can be recalculated from the user's target.</t>
+          <t>Requires editable drivers (#22) first. Then the target plan needs an input field for the driver headcount so ratios can be recalculated.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1496,13 +1712,13 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All changes in this PR target the Desktop React UI. Streamlit (manpower_app/ui_streamlit.py) was deliberately left out of scope.</t>
+          <t>All changes in this PR target the Desktop React UI. Streamlit (manpower_app/ui_streamlit.py) is deliberately out of scope.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1. Is Streamlit still a supported delivery surface, or is it being sunsetted in favor of the Tauri desktop / web container?
-2. If kept: do we mirror these UI changes (significant effort) or only the backend changes?</t>
+2. If kept: do we mirror these UI changes (significant effort) or only backend changes?</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1730,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Code currently lives at github.com/BahaaKaaki/manpower-optimization, public. README points to pwc-me-adv-strategyand/manpower-optimization as the canonical source. The Manpower.xlsx in the repo contains employee-level data.</t>
+          <t>Code currently lives at github.com/BahaaKaaki/manpower-optimization (public). README points to pwc-me-adv-strategyand/manpower-optimization as canonical source. Manpower.xlsx in the repo contains employee-level data.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1531,12 +1747,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The 94s → 19s win is from caching only. Remaining cost breakdown (cProfile): ~14s pandas .apply(axis=1) row iteration across 14 separate passes, ~6s openpyxl reading the .xlsx.</t>
+          <t>The 94s → 19s win is caching only. Remaining cost: ~14s pandas .apply(axis=1) row iteration across 14 separate passes, ~6s openpyxl XML parsing.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Two follow-up options:
+          <t>Options:
 1. Vectorize the cost calculations (replace row-wise apply with column-wise pandas ops). Bigger refactor, ~5-10× more savings on the apply path.
 2. Switch the Excel reader engine to calamine (python-calamine). One-line change in pipeline.py, ~3-5× speedup on the read path, adds one dependency.</t>
         </is>

--- a/docs/150526_enhancement_status.xlsx
+++ b/docs/150526_enhancement_status.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Items" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Open discussion points" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Round 2 status (current)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +70,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C7E9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00336B24"/>
+        <bgColor rgb="00336B24"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1761,4 +1775,735 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>What was done</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Scenario 6: Optimization fails when Risk factor = 0</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Removed the stale service-layer guard in manpower_app/service.py that raised ValueError when risk_factor &lt;= 0. The LP itself is R=0-safe; the constraint O*(1-R)+I&gt;=M degenerates to O+I&gt;=M (sound). End-to-end pytest scenario added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Scenario 5: Management Saudization rate ignored for 'Management' job family</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>'Management' is a distinct job family from 'Executive Management' in mappings.py. Added it to the profession_saudization_rates dict in service.py (both call sites). Per-profession Management rate now applies to BOTH families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Scenario 1: Tool prefers in-house when workbook outsourced cost is higher (safety officers)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Added cap_outsourced_at_inhouse() in costs.py. When the workbook's outsourced cost is higher than in-house non-Saudi (data inversion), it is capped at in-house so the LP can no longer ignore the outsourceability rule on cost grounds. Mirrors the Saudi premium clamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Scenario 8: Insurance + service margin not applied to all job families</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Two-part fix: (a) removed the legacy min(service_margin, 500) clamp in costs.py that silently truncated workbook values; (b) the negotiated-cost formula now falls back to Avg Cost Outsourced when 'Excluding Insurance Service' is NA, so insurance+margin reach families that have no subcontractor rows in the payroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Scenario 8 follow-up: cost-inversion cap must not break user-driven negotiated rates</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Moved the cost-inversion cap to apply BEFORE negotiated insurance+margin are added. The user can still legitimately push outsourced above in-house via the scenario knob; the cap only fixes raw workbook data inversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Saudization toggle on/off should disable the rate slider when off</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Slider is greyed out when 'Enforce overall Saudization' is off (parallel to the existing tenure-protection pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic Saudi protection percentage (not 0/100% only)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Replaced the binary can_reduce_current_saudi with protect_current_saudi_percent (0.0-1.0). The LP's _saudi_lower_bound uses round(current_saudi * pct) when supplied. Legacy boolean preserved for back-compat. UI surfaces it as a percentage input with sensible defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Output bars: legend with IS / IN / O short codes</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Bar segments use the short codes (In-house Saudi / In-house Non-Saudi / Outsourced) so the label fits even on the narrowest slices. A legend row above each family bar group explains the codes once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Pre/post Saudization rate under the donut charts</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>In Optimize Current Manpower mode, each donut now shows the Saudization % beneath: Current Saudization X% on the left, Optimized Saudization Y% on the right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Move Optimization Mode selection to right after Data Upload (was inside User Assumptions)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>New 'Optimization Mode' stage inserted between Data Upload and Additional Inputs. Two large radio cards (Optimize Current vs Target Manpower Plan). Removed the duplicate mode block from User Assumptions. Fixes Saad's 'jump back one step' UX note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>BU Selection workflow stage (#4 + #17)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>New 'BU Selection' step between Home and Data Upload. Tile grid with the 9 CPC subsidiaries (MGIC seeded as preconfigured by default; others empty until the user uploads their config). Click any tile to open its Configuration view; the 'Use this BU' button activates it and advances to Data Upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Map a new profession to an EXISTING job family on the Mappings step</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>When the uploaded payroll has an unmapped pair (e.g. 'Quarries - Senior Labor'), the user can now route it to an existing canonical family ('Skilled Labor') with a dropdown alongside the existing 'Define new job family' wizard. Persisted as payroll_pair_overrides; replayed on re-upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>BU Configuration via Excel (read-only UI viewer)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Per-BU Configuration panel shows the BU's outsourceability, ratios, and drivers in read-only tables. Excel is the SINGLE source of truth for editing; the user downloads the workbook, edits, and re-uploads. Single 'Value' column per row (no Default/Override duality). Sticky section navigator at the top with jump-anchors so 39 outsourceability rows do not hide the other sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>BU Configuration applies to optimization end-to-end</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Backend: rules.py exposes get_outsourceability_rules(overrides) and get_maximum_ratio_rules(overrides); ratios.py:calculate_driver_values accepts driver_overrides. prepare_model_data re-derives Outsourceability Type, Maximum Ratio, Driver Value, and Minimum Headcount Needed per family when overrides are supplied. Streamlit unaffected via defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>MGIC ships preconfigured; other BUs start empty</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>BUConfigurationPanel auto-seeds MGIC's configuration on first open from /assumptions/defaults. Other BUs (UAAC, FAST, SACODECO, Sphinx, Premco Precast, Premco Ready Mix, Bahra Steel, UCC) show the empty state with a 'Download starter Excel' CTA until the user uploads BU-specific values. The starter Excel lists every canonical family in column A with a blank Value column to fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Excel template validation (no silent partial saves)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>parse_workbook validates each row: outsourceability values must be one of the 3 canonical strings, ratios must match the '1:N' pattern, ratios with whitespace are normalized. Invalid rows are reported with row-level error messages and never silently applied. Tested for mixed valid/invalid input, missing sheets, and legacy back-compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saudi pay premium / outsource discount belong in User Assumptions (scenario), not BU Excel</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Removed the 'Engine Knobs' sheet from the BU workbook entirely. Saudi pay premium and Outsource cost discount are now scenario knobs on User Assumptions only. The BU workbook now has 4 sheets: README, Outsourceability, Ratios, Drivers (true per-BU constraints only). Legacy workbooks with the old Engine Knobs sheet still parse correctly (back-compat preserved).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Renamed 'Saudi cost premium' to 'Saudi pay premium' for client clarity</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Clearer label for the multiplier applied to non-Saudi in-house cost (e.g. 1.10x means Saudis cost 10% more). Internal field name unchanged to avoid breaking persistence/legacy payloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>BU Selection page polished and compact (all 9 BUs on one screen)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Hero header with CPC Holding mark + title. 3x3 card grid (responsive: 2-col tablet, 1-col phone). Each card shows: status pill (Custom configured / Using tool defaults), logo plate, BU code + full name, CTA + animated arrow. Stagger fade-up entry animation; hover lift + logo scale + accent border. No scroll: hero ~80px + 3 rows of ~180px cards fits comfortably.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>BU logos sourced from cpcholding.com</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Done with caveat</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Downloaded real high-quality logos from cpcholding.com for MGIC, UAAC, SACODECO, FAST, Premco Precast, Premco Ready Mix, Bahra Steel. Sphinx, UCC, and a dark-on-light CPC Holding mark were not found at acceptable quality online. Currently all logos are temporarily disabled per consultant request; every BU tile renders a clean typographic placeholder (BU code in display-serif) until proper brand assets are dropped into desktop/src/assets/bu-logos/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Configuration panel: 'Edit configuration via Excel' redesigned</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Two-step card layout (Step 1: Download, Step 2: Upload) with icons, numbered step pills, hover/lift animations. The upload card is a drag-and-drop zone (drop your .xlsx anywhere in the card) with active-drag visual feedback. Validation errors shown inline; status banner above/below indicates success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Removed all em-dashes from user-facing copy</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Replaced em-dashes with periods, commas, or colons across BUSelectionWorkspace, MappingResolveWorkspace, ScenarioControls, ResultsDashboard, AppShell, and supporting copy. Cleaner reading flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Removed duplicate 'Continue' / 'Next' buttons</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>The AppShell renders a Previous/Next stage navigator at the bottom of every step. Removed redundant inline 'Continue to User Assumptions' on the Mappings step and 'Continue to Additional Inputs' on the Mode step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>9 Debugging-sheet scenarios codified as pytest regressions</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>tests/test_optimization.py has DebuggingScenarioTests covering Scenarios 1, 5, 6, 8 + helper tests for the fixed behaviors. Future code changes can no longer silently re-introduce any of these consultant-reported bugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>End-to-end user journey + edge-case coverage</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Test suite expanded to 56 tests across 14 classes (3 skip on this machine because they require the consultant's local workbook fixture). Covers: BU overrides reaching the LP, BU isolation, target mode + BU overrides combined, target mode + scenario cost knobs combined, Excel round-trip with mixed valid/invalid rows, HTTP wire-layer smoke tests for /health, /assumptions/defaults, /bu/configuration/*, and the full upload-then-optimize cycle over JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Hi-res CPC logo (high-quality dark version on transparent background)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Only the white-on-transparent variant is available on cpcholding.com (not usable on light backgrounds). Need Saad to share a proper transparent-background dark mark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>'How the tool works' / Help tab</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Per the consultant's workbook note, this needs Tarek (principal) alignment before we build it. Not in scope this round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Sphinx, UCC individual logos + dark CPC Holding mark</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Not on the current cpcholding.com portfolio (UCC, Sphinx) or only available as white-on-transparent (CPC). Drop high-quality PNGs into desktop/src/assets/bu-logos/ and add the logoSrc field in BUSelectionWorkspace.tsx to wire them in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Saudization rates as BU constraints (vs scenario knobs)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Saad's original spec grouped Saudization under User Assumptions, but it could arguably live in BU configuration as a regulatory constraint per industry. Not changed in this round; kept as scenario inputs. Easy to move later if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Frontend UI click-automation (Playwright/Cypress)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Optimizer logic, HTTP wire layer, and Python data flow are all auto-tested. UI rendering and button wiring are verified via in-browser smoke testing. Adding automated UI tests is recommended before client handoff but is a separate effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Streamlit changes</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Same scope as PR #1. The rules.py refactor preserves module-level constants for back-compat so Streamlit continues to work unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-18 - 150526 batch 2 enhancements (consolidated update).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>